--- a/src/test/resources/excel/annual_leave_test.xlsx
+++ b/src/test/resources/excel/annual_leave_test.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jinhy\Projects\BackEnd\src\test\resources\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18846A72-781A-414B-B17B-3A5AAE0E813A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E14D30-4D79-49A8-BC08-CF084F339AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47430" yWindow="11895" windowWidth="21600" windowHeight="11055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="8월" sheetId="52" r:id="rId1"/>
+    <sheet name="8월" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'8월'!$A$1:$K$41</definedName>
@@ -21,9 +21,6 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -40,74 +37,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="16">
+  <si>
+    <t>&lt; 2025년 8월 연차휴가 사용/잔여 현황 &gt;</t>
+  </si>
+  <si>
+    <t>기준일 : 2025-12-01</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
   <si>
     <t>소  속</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>비고</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>성 명</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>입사일</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>어썸리드</t>
-  </si>
-  <si>
-    <t>어썸리드</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>발생
 연차</t>
   </si>
   <si>
-    <t>■ 기타사항</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>2025
 월차</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2024
 이월월차</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용</t>
+  </si>
+  <si>
+    <t>잔여일</t>
+  </si>
+  <si>
+    <t>비고</t>
+  </si>
+  <si>
+    <t>어썸리드</t>
+  </si>
+  <si>
+    <t>■ 기타사항</t>
   </si>
   <si>
     <t>1년 미만자의 경우 2025년도 연차를 미리 부여해준것임으로 1년미만 근무 후 퇴사시 (-)공제처리 될 수 있음</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>NO</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>사용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>잔여일</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt; 2025년 8월 연차휴가 사용/잔여 현황 &gt;</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>기준일 : 2025-12-01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트 유저</t>
+    <t>관리자</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -115,7 +95,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -137,12 +117,6 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="굴림체"/>
-      <family val="2"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
@@ -261,21 +235,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top style="hair">
         <color indexed="64"/>
       </top>
@@ -393,9 +352,7 @@
       <top style="hair">
         <color indexed="64"/>
       </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -408,13 +365,11 @@
       <top style="hair">
         <color indexed="64"/>
       </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -423,7 +378,35 @@
       <top style="hair">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -433,10 +416,10 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
+      <top/>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -446,10 +429,8 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -464,17 +445,6 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="double">
         <color indexed="64"/>
       </bottom>
@@ -488,144 +458,143 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -634,15 +603,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FF0000CC"/>
-      <color rgb="FF00FFCC"/>
-      <color rgb="FF9999FF"/>
-      <color rgb="FFFF99FF"/>
-      <color rgb="FFFFFFCC"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -652,94 +612,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>44823</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>33617</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3695884" cy="491417"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="168648" y="738467"/>
-          <a:ext cx="3695884" cy="491417"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>※ 8</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>월달</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1800" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> 사용내역 포함 안되어있음</a:t>
-          </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1800">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1004,7 +876,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:L42"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
@@ -1016,22 +888,23 @@
     <col min="6" max="10" width="9.375" style="1" customWidth="1"/>
     <col min="11" max="11" width="15.125" style="2" customWidth="1"/>
     <col min="12" max="12" width="3.625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="13" max="13" width="9" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="37.15" x14ac:dyDescent="0.6">
-      <c r="B2" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
+    <row r="2" spans="2:12" ht="37.15" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B2" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="45"/>
       <c r="L2" s="5"/>
     </row>
     <row r="3" spans="2:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -1060,59 +933,59 @@
       <c r="K4" s="14"/>
     </row>
     <row r="5" spans="2:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="J5" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" s="39"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="J5" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="34"/>
     </row>
     <row r="6" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="42" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="K6" s="35" t="s">
-        <v>1</v>
-      </c>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B7" s="41"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="36"/>
+    <row r="7" spans="2:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="B7" s="47"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
+      <c r="K7" s="40"/>
       <c r="L7" s="4"/>
     </row>
     <row r="8" spans="2:12" ht="24.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.6">
@@ -1120,13 +993,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" s="17">
-        <v>46022</v>
+        <v>45658</v>
       </c>
       <c r="F8" s="6">
         <v>18</v>
@@ -1148,7 +1021,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="21"/>
@@ -1164,7 +1037,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="17"/>
@@ -1180,7 +1053,7 @@
         <v>4</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="17"/>
@@ -1196,7 +1069,7 @@
         <v>5</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="21"/>
@@ -1212,7 +1085,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="21"/>
@@ -1228,7 +1101,7 @@
         <v>7</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="21"/>
@@ -1244,7 +1117,7 @@
         <v>8</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="17"/>
@@ -1260,7 +1133,7 @@
         <v>9</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="21"/>
@@ -1276,7 +1149,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="21"/>
@@ -1292,7 +1165,7 @@
         <v>11</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="17"/>
@@ -1308,7 +1181,7 @@
         <v>12</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="17"/>
@@ -1324,7 +1197,7 @@
         <v>13</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="21"/>
@@ -1340,7 +1213,7 @@
         <v>14</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D21" s="30"/>
       <c r="E21" s="17"/>
@@ -1356,7 +1229,7 @@
         <v>15</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="17"/>
@@ -1372,7 +1245,7 @@
         <v>16</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="17"/>
@@ -1388,7 +1261,7 @@
         <v>17</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="17"/>
@@ -1404,7 +1277,7 @@
         <v>18</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D25" s="13"/>
       <c r="E25" s="21"/>
@@ -1420,7 +1293,7 @@
         <v>19</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="21"/>
@@ -1436,7 +1309,7 @@
         <v>20</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D27" s="13"/>
       <c r="E27" s="21"/>
@@ -1452,7 +1325,7 @@
         <v>21</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="17"/>
@@ -1468,7 +1341,7 @@
         <v>22</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="17"/>
@@ -1484,7 +1357,7 @@
         <v>23</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="17"/>
@@ -1500,7 +1373,7 @@
         <v>24</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D31" s="13"/>
       <c r="E31" s="21"/>
@@ -1516,7 +1389,7 @@
         <v>25</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="17"/>
@@ -1532,7 +1405,7 @@
         <v>26</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D33" s="32"/>
       <c r="E33" s="21"/>
@@ -1548,7 +1421,7 @@
         <v>27</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D34" s="32"/>
       <c r="E34" s="21"/>
@@ -1564,7 +1437,7 @@
         <v>28</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D35" s="30"/>
       <c r="E35" s="17"/>
@@ -1580,7 +1453,7 @@
         <v>29</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D36" s="30"/>
       <c r="E36" s="17"/>
@@ -1596,7 +1469,7 @@
         <v>30</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D37" s="30"/>
       <c r="E37" s="17"/>
@@ -1612,7 +1485,7 @@
         <v>31</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D38" s="30"/>
       <c r="E38" s="17"/>
@@ -1628,7 +1501,7 @@
         <v>32</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D39" s="31"/>
       <c r="E39" s="27"/>
@@ -1639,14 +1512,14 @@
       <c r="J39" s="28"/>
       <c r="K39" s="29"/>
     </row>
-    <row r="40" spans="2:11" ht="19.149999999999999" x14ac:dyDescent="0.6">
+    <row r="40" spans="2:11" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B40" s="10" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B41" s="11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.6">
@@ -1654,24 +1527,23 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="B6:B7"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="B6:B7"/>
     <mergeCell ref="F6:F7"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="I6:I7"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="H6:H7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="J6:J7"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0" right="0" top="0" bottom="0" header="0.19685039370078741" footer="0.15748031496062992"/>
-  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0.19685039370078741" footer="0.15748031496062989"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait"/>
 </worksheet>
 </file>